--- a/docs/plano-de-tagueamento-banco-nuzzi.xlsx
+++ b/docs/plano-de-tagueamento-banco-nuzzi.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elementos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eventos'!$A$1:$S$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eventos'!$A$1:$T$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parâmetros'!$A$1:$I$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Banners'!$A$1:$H$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Telas'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mapa de tagueamento'!$A$1:$H$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mapa de tagueamento'!$A$1:$K$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Jornadas'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Elementos'!$A$1:$E$18</definedName>
   </definedNames>
@@ -178,6 +178,1786 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -469,7 +2249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -491,6 +2271,7 @@
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -587,6 +2368,11 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Descrição completa para a IA</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Elementos no app (IDs do Mapa de tagueamento)</t>
         </is>
       </c>
     </row>
@@ -699,6 +2485,11 @@
 Técnico: window.hashchange + abertura do app em Todas; route(), depois de mostrar a tela.</t>
         </is>
       </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>EL-01, EL-04, EL-05, EL-13, EL-15, EL-16, EL-17, EL-22, EL-23, EL-26, EL-27, EL-28, EL-32, EL-33, EL-40, EL-41, EL-42, EL-43, EL-44, EL-46, EL-47, EL-53, EL-55, EL-62, EL-67, EL-68, EL-69, EL-70, EL-71</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -808,6 +2599,11 @@
 Técnico: [data-promo] em /acesso, /inicio, /cartoes; impression(), chamada pelo IntersectionObserver.</t>
         </is>
       </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>EL-10, EL-12, EL-14, EL-35, EL-37, EL-39, EL-59</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -917,6 +2713,11 @@
 Técnico: [data-promo] .promo-cta em /acesso, /inicio, /cartoes; listener global de clique, ramo .promo-cta.</t>
         </is>
       </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>EL-11, EL-13, EL-15, EL-36, EL-38, EL-40, EL-60</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1026,6 +2827,11 @@
 Técnico: [data-carousel] .track, .dot em /acesso, /inicio; clique num indicador (.dot) do carrossel.</t>
         </is>
       </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>EL-09, EL-34</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1135,6 +2941,11 @@
 Técnico: [data-track] (lista na aba Elementos) em Todas; listener global de clique, ramo [data-track].</t>
         </is>
       </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>EL-04, EL-05, EL-17, EL-27, EL-28, EL-32, EL-33, EL-41, EL-42, EL-43, EL-47, EL-53, EL-67, EL-68, EL-69, EL-70, EL-71</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1242,6 +3053,11 @@
 Técnico: Rotas protegidas (#inicio, #extrato, #pix, #cartoes, #investimentos) em /acesso e telas logadas; route(), tela logada aberta sem login.</t>
         </is>
       </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>EL-05, EL-13, EL-15</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1349,6 +3165,11 @@
 Técnico: #keypad [data-key] em /entrar; pressKey(), primeiro dígito da senha.</t>
         </is>
       </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>EL-18</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1454,6 +3275,11 @@
 Uso em análise: Taxa de erro do login por error_type.
 Propriedades principais: form_id, error_type.
 Técnico: #btn-entrar em /entrar; loginFail(), chamada por submitLogin() quando a senha é recusada.</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>EL-20, EL-21</t>
         </is>
       </c>
     </row>
@@ -1564,6 +3390,11 @@
 Técnico: #btn-entrar em /entrar; submitLogin(), ramo de sucesso.</t>
         </is>
       </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>EL-22</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1670,6 +3501,11 @@
 Técnico: #btn-sair em /inicio; listener de clique de #btn-sair.</t>
         </is>
       </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>EL-26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1776,6 +3612,11 @@
 Técnico: #btn-saldo em /inicio; listener global de clique, ramo data-action=toggle_balance.</t>
         </is>
       </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>EL-24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1882,6 +3723,11 @@
 Técnico: [data-filter] em /extrato; listener de clique de [data-filter].</t>
         </is>
       </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>EL-45</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1989,6 +3835,11 @@
 Técnico: [data-action=quick_action] em /acesso, /entrar, /inicio, /cartoes; listener global de clique, ramo data-action=quick_action.</t>
         </is>
       </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>EL-02, EL-03, EL-06, EL-07, EL-19, EL-25, EL-29, EL-30, EL-31, EL-56, EL-57, EL-58</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2095,6 +3946,11 @@
 Técnico: [data-action=offer_accept] em /inicio; listener global de clique, ramo data-action=offer_accept.</t>
         </is>
       </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>EL-36, EL-38</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2201,6 +4057,11 @@
 Técnico: [data-action=card_request] em /cartoes; listener global de clique, ramo data-action=card_request.</t>
         </is>
       </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>EL-60, EL-61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2307,6 +4168,11 @@
 Técnico: [data-action=investment_intent] em /investimentos; listener global de clique, ramo data-action=investment_intent.</t>
         </is>
       </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>EL-63, EL-64, EL-65, EL-66</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2414,6 +4280,11 @@
 Técnico: [data-action=lead] em /acesso; listener global de clique, ramo data-action=lead.</t>
         </is>
       </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>EL-08, EL-11</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2520,6 +4391,11 @@
 Técnico: #pix-form (focusin) em /pix; listener focusin de #pix-form.</t>
         </is>
       </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>EL-48</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2624,6 +4500,11 @@
 Uso em análise: Perda no funil de Pix por error_type.
 Propriedades principais: error_type.
 Técnico: #pix-form (submit) em /pix; listener submit de #pix-form, ramo de erro.</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>EL-49</t>
         </is>
       </c>
     </row>
@@ -2734,6 +4615,11 @@
 Técnico: #pix-form (submit válido) em /pix; listener submit de #pix-form, ramo de sucesso.</t>
         </is>
       </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>EL-50</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2838,6 +4724,11 @@
 Uso em análise: Atrito na tela de revisão do Pix.
 Propriedades principais: step.
 Técnico: #pix-corrigir em /pix; listener de clique de #pix-corrigir.</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>EL-52</t>
         </is>
       </c>
     </row>
@@ -2949,6 +4840,11 @@
 Técnico: #pix-confirmar em /pix; listener de clique de #pix-confirmar.</t>
         </is>
       </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>EL-51</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3054,9 +4950,14 @@
 Técnico: #pix-novo em /pix; listener de clique de #pix-novo.</t>
         </is>
       </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>EL-54</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S24"/>
+  <autoFilter ref="A1:T24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6165,2818 +8066,3618 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Tela</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Área da tela</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Elemento (o que o cliente vê)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Seletor no código</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gesto</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Eventos disparados, em ordem</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valores fixos enviados</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Arquivo do print</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Print (elemento destacado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="312.75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>EL-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Tela inteira</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Tela de acesso</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>[data-page=acesso]</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Abrir o app deslogado</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>page_view</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>page_path=/acesso · page_type=publico · login_status=logged_out</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-01.jpg</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="312.75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>EL-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Topo</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Ícone de ajuda (?)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>[data-action=quick_action][data-item=ajuda]</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>action_id=ajuda · page_path=/acesso</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-02.jpg</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="312.75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>EL-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Conta salva</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Link Trocar</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>[data-item=trocar_conta]</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>action_id=trocar_conta · page_path=/acesso</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-03.jpg</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="312.75" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>EL-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Botão principal</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Acessar minha conta</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>[data-track=acesso_entrar]</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>item_id=acesso_entrar · content_type=cta · depois page_path=/entrar</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-04.jpg</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="312.75" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>EL-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>[data-track=acesso_pix]</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>select_content → auth_required → page_view</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>item_id=acesso_pix · target_path=/pix · depois page_path=/entrar</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Depois do login, o app abre o Pix direto.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-05.jpg</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="312.75" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>EL-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Token</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>[data-item=token]</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>action_id=token · page_path=/acesso</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-06.jpg</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="312.75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>EL-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Bloquear cartão</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>[data-item=bloquear_cartao]</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>action_id=bloquear_cartao · page_path=/acesso</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>O mesmo action_id existe na tela Cartões; separe por page_path.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-07.jpg</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="312.75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>EL-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Abrir conta</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>[data-action=lead]</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>generate_lead</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>lead_type=abertura_conta · page_path=/acesso</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Sem select_promotion, porque não é banner.</t>
         </is>
       </c>
-    </row>
-    <row r="10">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-08.jpg</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="312.75" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>EL-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Carrossel Para você</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Indicadores e arrasto</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>[data-carousel=acesso_destaques]</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Arrastar ou tocar no indicador</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>carousel_navigate</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>carousel_id=acesso_destaques · control=arrastar ou indicador</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-09.jpg</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="312.75" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>EL-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Carrossel Para você</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Banner Abra sua conta</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_abra_conta]</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Aparecer 60% na tela</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>view_promotion</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_abra_conta · creative_slot=acesso_destaque_1</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-10.jpg</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="312.75" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>EL-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Carrossel Para você</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Botão Quero abrir</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_abra_conta] .promo-cta</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>select_promotion → generate_lead</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_abra_conta · lead_type=abertura_conta</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-11.jpg</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="312.75" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>EL-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Carrossel Para você</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Banner Nuzzi Black</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_cartao_black]</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Aparecer 60% na tela</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>view_promotion</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_cartao_black · creative_slot=acesso_destaque_2</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-12.jpg</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="312.75" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>EL-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Carrossel Para você</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Botão Conhecer o Black</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_cartao_black] .promo-cta</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>select_promotion → auth_required → page_view</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_cartao_black · target_path=/cartoes · depois page_path=/entrar</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-13.jpg</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="312.75" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>EL-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Carrossel Para você</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Banner CDB 104% do CDI</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_cdb_liquidez]</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Aparecer 60% na tela</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>view_promotion</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_cdb_liquidez · creative_slot=acesso_destaque_3</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-14.jpg</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="312.75" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>EL-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>/acesso</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Carrossel Para você</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Botão Ver investimentos</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_cdb_liquidez] .promo-cta</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>select_promotion → auth_required → page_view</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_cdb_liquidez · target_path=/investimentos · depois page_path=/entrar</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-15.jpg</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="312.75" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>EL-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>/entrar</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Tela inteira</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tela de senha</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>[data-page=entrar]</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Abrir</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>page_view</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>page_path=/entrar · page_type=login</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-16.jpg</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="312.75" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>EL-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>/entrar</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Topo</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Seta Voltar</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>[data-track=senha_voltar]</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>item_id=senha_voltar · link_text=Voltar · depois page_path=/acesso</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-17.jpg</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="312.75" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>EL-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>/entrar</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Teclado</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Teclas de 0 a 9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>#keypad [data-key]</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Primeiro dígito</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>form_start</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>form_id=login · page_path=/entrar</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Só no primeiro dígito de cada visita.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-18.jpg</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="312.75" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>EL-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>/entrar</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Teclado</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Esqueci</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>[data-item=esqueci_senha]</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>action_id=esqueci_senha · page_path=/entrar</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-19.jpg</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="312.75" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>EL-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>/entrar</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Botão</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Entrar com menos de 6 dígitos</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>#btn-entrar</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>login_error</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>form_id=login · error_type=senha_incompleta</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-20.jpg</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="312.75" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>EL-21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>/entrar</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Botão</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Entrar com 000000</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>#btn-entrar</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>login_error</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>form_id=login · error_type=senha_incorreta</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Senha de teste que simula erro.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-21.jpg</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="312.75" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>EL-22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>/entrar</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Botão</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Entrar com 6 dígitos</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>#btn-entrar</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>login → page_view</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>method=senha_eletronica · user_id=u_8f2c41a9 · depois page_path do destino</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-22.jpg</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="312.75" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>EL-23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Tela inteira</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Início</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>[data-page=inicio]</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Abrir</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>page_view</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>page_path=/inicio · page_type=area_logada · user_id</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-23.jpg</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="312.75" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>EL-24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Topo</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Ícone de olho</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>#btn-saldo</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>toggle_balance</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>state=hidden ou visible</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>O valor do saldo não é enviado.</t>
         </is>
       </c>
-    </row>
-    <row r="26">
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-24.jpg</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="312.75" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>EL-25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Topo</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sino de notificações</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>[data-item=notificacoes]</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>action_id=notificacoes · page_path=/inicio</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-25.jpg</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="312.75" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>EL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Topo</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Ícone Sair</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>#btn-sair</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>logout → page_view</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>user_id · depois page_path=/acesso · login_status=logged_out</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-26.jpg</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="312.75" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>EL-27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Saldo</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Ver extrato</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>[data-track=inicio_ver_extrato]</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>item_id=inicio_ver_extrato · depois page_path=/extrato</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-27.jpg</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="312.75" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>EL-28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>[data-track=atalho_pix]</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>item_id=atalho_pix · content_type=shortcut · depois page_path=/pix</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-28.jpg</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="312.75" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>EL-29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Pagar</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>[data-item=pagar_boleto]</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>action_id=pagar_boleto · page_path=/inicio</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-29.jpg</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="312.75" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>EL-30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Transferir</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>[data-item=transferir]</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>action_id=transferir · page_path=/inicio</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-30.jpg</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="312.75" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>EL-31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Recarga</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>[data-item=recarga]</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>action_id=recarga · page_path=/inicio</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-31.jpg</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="312.75" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>EL-32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Cartões</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>[data-track=atalho_cartoes]</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>item_id=atalho_cartoes · depois page_path=/cartoes</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-32.jpg</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="312.75" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>EL-33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Atalhos</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>[data-track=atalho_investir]</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>item_id=atalho_investir · depois page_path=/investimentos</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-33.jpg</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="312.75" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>EL-34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Carrossel de ofertas</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Indicadores e arrasto</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>[data-carousel=inicio_ofertas]</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Arrastar ou tocar no indicador</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>carousel_navigate</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>carousel_id=inicio_ofertas · control=arrastar ou indicador</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-34.jpg</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="312.75" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>EL-35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Carrossel de ofertas</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Banner Crédito pré-aprovado</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_credito_preaprovado]</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Aparecer 60% na tela</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>view_promotion</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_credito_preaprovado · creative_slot=inicio_oferta_1</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-35.jpg</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="312.75" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>EL-36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Carrossel de ofertas</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Botão Simular parcelas</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_credito_preaprovado] .promo-cta</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>select_promotion → offer_click</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_credito_preaprovado · offer_id=credito_preaprovado</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>offer_click está em Ajustar (sinal duplicado).</t>
         </is>
       </c>
-    </row>
-    <row r="38">
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-36.jpg</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="312.75" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>EL-37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Carrossel de ofertas</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Banner Seguro cartão</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_seguro_cartao]</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Aparecer 60% na tela</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>view_promotion</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_seguro_cartao · creative_slot=inicio_oferta_2</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-37.jpg</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="312.75" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>EL-38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Carrossel de ofertas</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Botão Contratar seguro</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_seguro_cartao] .promo-cta</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>select_promotion → offer_click</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_seguro_cartao · offer_id=seguro_cartao</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-38.jpg</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="312.75" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>EL-39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Carrossel de ofertas</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Banner Pix agendado</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_pix_agendado]</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Aparecer 60% na tela</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>view_promotion</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_pix_agendado · creative_slot=inicio_oferta_3</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-39.jpg</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="312.75" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>EL-40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Carrossel de ofertas</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Botão Agendar um Pix</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_pix_agendado] .promo-cta</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>select_promotion → page_view</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_pix_agendado · depois page_path=/pix</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-40.jpg</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="312.75" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>EL-41</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Cartão da fatura</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Cartão Nuzzi Mais (fatura)</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>[data-track=inicio_card_fatura]</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>item_id=inicio_card_fatura · link_text=Cartão Nuzzi Mais · depois page_path=/cartoes</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>link_text fixo: o valor da fatura não vai.</t>
         </is>
       </c>
-    </row>
-    <row r="43">
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-41.jpg</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="312.75" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>EL-42</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Últimos lançamentos</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Ver tudo</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>[data-track=inicio_extrato_completo]</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>item_id=inicio_extrato_completo · depois page_path=/extrato</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-42.jpg</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="312.75" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>EL-43</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>/inicio</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Investimentos</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Cartão de investimentos</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>[data-track=inicio_card_investimentos]</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>item_id=inicio_card_investimentos · link_text=Investimentos · depois page_path=/investimentos</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>link_text fixo: o total investido não vai.</t>
         </is>
       </c>
-    </row>
-    <row r="45">
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-43.jpg</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="312.75" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>EL-44</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>/extrato</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Tela inteira</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Extrato</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>[data-page=extrato]</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Abrir</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>page_view</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>page_path=/extrato</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-44.jpg</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="312.75" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>EL-45</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>/extrato</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Filtros</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tudo, Entradas, Saídas</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>[data-filter]</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Toque num filtro diferente do atual</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>statement_filter</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>filter=todos, entradas ou saidas</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Os lançamentos não são enviados.</t>
         </is>
       </c>
-    </row>
-    <row r="47">
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-45.jpg</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="312.75" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>EL-46</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Tela inteira</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>[data-page=pix]</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Abrir</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>page_view</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>page_path=/pix</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-46.jpg</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="312.75" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>EL-47</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Topo</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Seta Voltar</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>[data-track=pix_voltar]</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>item_id=pix_voltar · depois page_path=/inicio</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-47.jpg</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="312.75" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>EL-48</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Etapa 1 · Dados</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Campos chave, valor e mensagem</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>#pix-form</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Primeiro foco num campo</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>pix_start</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>page_path=/pix</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>Uma vez a cada abertura do Pix.</t>
         </is>
       </c>
-    </row>
-    <row r="50">
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-48.jpg</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="312.75" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>EL-49</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Etapa 1 · Dados</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Botão Continuar com erro</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>#pix-form [type=submit]</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>pix_error</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>error_type=chave_vazia, valor_invalido ou saldo_insuficiente</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-49.jpg</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="312.75" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>EL-50</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Etapa 1 · Dados</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Botão Continuar válido</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>#pix-form [type=submit]</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>pix_review</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>value · currency=BRL · pix_key_type</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>A chave nunca é enviada.</t>
         </is>
       </c>
-    </row>
-    <row r="52">
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-50.jpg</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="312.75" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>EL-51</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Etapa 2 · Revisão</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Botão Confirmar Pix</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>#pix-confirmar</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>pix_success</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>transaction_id · value · currency=BRL · pix_key_type</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-51.jpg</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="312.75" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>EL-52</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Etapa 2 · Revisão</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Botão Corrigir dados</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>#pix-corrigir</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>pix_edit</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>step=revisao</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-52.jpg</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="312.75" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>EL-53</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Etapa 3 · Comprovante</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Voltar ao início</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>[data-track=pix_comprovante_inicio]</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>item_id=pix_comprovante_inicio · depois page_path=/inicio</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-53.jpg</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="312.75" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>EL-54</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>/pix</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Etapa 3 · Comprovante</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fazer outro Pix</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>#pix-novo</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>pix_restart</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>(nenhum parâmetro)</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-54.jpg</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="312.75" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>EL-55</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>/cartoes</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Tela inteira</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Cartões</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>[data-page=cartoes]</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Abrir</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>page_view</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>page_path=/cartoes</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-55.jpg</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="312.75" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>EL-56</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>/cartoes</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Ações do cartão</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Cartão virtual</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>[data-item=cartao_virtual]</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>action_id=cartao_virtual · page_path=/cartoes</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-56.jpg</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="312.75" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>EL-57</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>/cartoes</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Ações do cartão</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Bloquear</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>[data-item=bloquear_cartao]</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>action_id=bloquear_cartao · page_path=/cartoes</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-57.jpg</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="312.75" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>EL-58</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>/cartoes</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Ações do cartão</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Ajustar limite</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>[data-item=ajustar_limite]</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>quick_action</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>action_id=ajustar_limite · page_path=/cartoes</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-58.jpg</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="312.75" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>EL-59</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>/cartoes</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Oferta</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Banner Troque para o Nuzzi Black</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_upgrade_black]</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Aparecer 60% na tela</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>view_promotion</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_upgrade_black · creative_slot=cartoes_oferta_1</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-59.jpg</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="312.75" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>EL-60</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>/cartoes</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Oferta</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Botão Pedir o Black</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>[data-promo=bnr_upgrade_black] .promo-cta</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>select_promotion → card_request</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>promotion_id=bnr_upgrade_black · card_tier=black</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-60.jpg</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="312.75" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>EL-61</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>/cartoes</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Cartão adicional</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Botão Pedir adicional</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>[data-action=card_request][data-item=adicional]</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>card_request</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>card_tier=adicional</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>Sem select_promotion, porque não é banner.</t>
         </is>
       </c>
-    </row>
-    <row r="63">
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-61.jpg</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="312.75" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>EL-62</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>/investimentos</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Tela inteira</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Investimentos</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>[data-page=investimentos]</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Abrir</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>page_view</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>page_path=/investimentos</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-62.jpg</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="312.75" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>EL-63</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>/investimentos</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Renda fixa</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Investir · CDB Liquidez Diária</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>[data-item=cdb_liquidez]</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>investment_intent</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>product_id=cdb_liquidez</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-63.jpg</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="312.75" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>EL-64</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>/investimentos</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Renda fixa</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Investir · LCI 90 dias</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>[data-item=lci_90]</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>investment_intent</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>product_id=lci_90</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-64.jpg</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="312.75" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>EL-65</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>/investimentos</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Renda fixa</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Investir · CDB 2 anos</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>[data-item=cdb_ipca_2a]</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>investment_intent</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>product_id=cdb_ipca_2a</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-65.jpg</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="312.75" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>EL-66</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>/investimentos</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Renda fixa</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Investir · Fundo Nuzzi DI</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>[data-item=fundo_di]</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>investment_intent</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>product_id=fundo_di</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-66.jpg</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="312.75" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>EL-67</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>Telas logadas</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Barra de abas</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Início</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>[data-track=tab_inicio]</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>item_id=tab_inicio · content_type=tab_bar · depois page_path=/inicio</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>Aparece em /inicio, /extrato, /pix, /cartoes e /investimentos.</t>
         </is>
       </c>
-    </row>
-    <row r="69">
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-67.jpg</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="312.75" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>EL-68</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>Telas logadas</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Barra de abas</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Extrato</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>[data-track=tab_extrato]</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>item_id=tab_extrato · depois page_path=/extrato</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-68.jpg</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="312.75" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>EL-69</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>Telas logadas</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Barra de abas</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Pix</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>[data-track=tab_pix]</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>item_id=tab_pix · depois page_path=/pix</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-69.jpg</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="312.75" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>EL-70</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>Telas logadas</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Barra de abas</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Cartões</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>[data-track=tab_cartoes]</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>item_id=tab_cartoes · depois page_path=/cartoes</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-70.jpg</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="312.75" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>EL-71</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>Telas logadas</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Barra de abas</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>[data-track=tab_investir]</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>select_content → page_view</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>item_id=tab_investir · depois page_path=/investimentos</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>docs/prints/EL-71.jpg</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H72"/>
+  <autoFilter ref="A1:K72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/docs/plano-de-tagueamento-banco-nuzzi.xlsx
+++ b/docs/plano-de-tagueamento-banco-nuzzi.xlsx
@@ -189,7 +189,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -214,7 +214,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -239,7 +239,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -264,7 +264,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -289,7 +289,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -314,7 +314,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -339,7 +339,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -364,7 +364,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1981200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -389,7 +389,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -414,7 +414,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -439,7 +439,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -464,7 +464,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -489,7 +489,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -514,7 +514,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -539,7 +539,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -564,7 +564,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -589,7 +589,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -614,7 +614,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1771650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -639,7 +639,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -664,7 +664,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -689,7 +689,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -714,7 +714,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -739,7 +739,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -764,7 +764,7 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -789,7 +789,7 @@
       <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -814,7 +814,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -839,7 +839,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -864,7 +864,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -889,7 +889,7 @@
       <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -914,7 +914,7 @@
       <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -939,7 +939,7 @@
       <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -964,7 +964,7 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -989,7 +989,7 @@
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1014,7 +1014,7 @@
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1039,7 +1039,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1064,7 +1064,7 @@
       <row>36</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1089,7 +1089,7 @@
       <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1114,7 +1114,7 @@
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="38" name="Image 38" descr="Picture"/>
@@ -1139,7 +1139,7 @@
       <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1164,7 +1164,7 @@
       <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1189,7 +1189,7 @@
       <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="41" name="Image 41" descr="Picture"/>
@@ -1214,7 +1214,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1239,7 +1239,7 @@
       <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1264,7 +1264,7 @@
       <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="44" name="Image 44" descr="Picture"/>
@@ -1289,7 +1289,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -1314,7 +1314,7 @@
       <row>46</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="46" name="Image 46" descr="Picture"/>
@@ -1339,7 +1339,7 @@
       <row>47</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="47" name="Image 47" descr="Picture"/>
@@ -1364,7 +1364,7 @@
       <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="2609850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="48" name="Image 48" descr="Picture"/>
@@ -1389,7 +1389,7 @@
       <row>49</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>
@@ -1414,7 +1414,7 @@
       <row>50</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="50" name="Image 50" descr="Picture"/>
@@ -1439,7 +1439,7 @@
       <row>51</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="51" name="Image 51" descr="Picture"/>
@@ -1464,7 +1464,7 @@
       <row>52</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="52" name="Image 52" descr="Picture"/>
@@ -1489,7 +1489,7 @@
       <row>53</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="53" name="Image 53" descr="Picture"/>
@@ -1514,7 +1514,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="54" name="Image 54" descr="Picture"/>
@@ -1539,7 +1539,7 @@
       <row>55</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="55" name="Image 55" descr="Picture"/>
@@ -1564,7 +1564,7 @@
       <row>56</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="56" name="Image 56" descr="Picture"/>
@@ -1589,7 +1589,7 @@
       <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="57" name="Image 57" descr="Picture"/>
@@ -1614,7 +1614,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="58" name="Image 58" descr="Picture"/>
@@ -1639,7 +1639,7 @@
       <row>59</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="59" name="Image 59" descr="Picture"/>
@@ -1664,7 +1664,7 @@
       <row>60</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="60" name="Image 60" descr="Picture"/>
@@ -1689,7 +1689,7 @@
       <row>61</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="61" name="Image 61" descr="Picture"/>
@@ -1714,7 +1714,7 @@
       <row>62</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="4667250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="62" name="Image 62" descr="Picture"/>
@@ -1739,7 +1739,7 @@
       <row>63</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="63" name="Image 63" descr="Picture"/>
@@ -1764,7 +1764,7 @@
       <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="64" name="Image 64" descr="Picture"/>
@@ -1789,7 +1789,7 @@
       <row>65</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="65" name="Image 65" descr="Picture"/>
@@ -1814,7 +1814,7 @@
       <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="66" name="Image 66" descr="Picture"/>
@@ -1839,7 +1839,7 @@
       <row>67</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="67" name="Image 67" descr="Picture"/>
@@ -1864,7 +1864,7 @@
       <row>68</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="68" name="Image 68" descr="Picture"/>
@@ -1889,7 +1889,7 @@
       <row>69</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="69" name="Image 69" descr="Picture"/>
@@ -1914,7 +1914,7 @@
       <row>70</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="70" name="Image 70" descr="Picture"/>
@@ -1939,7 +1939,7 @@
       <row>71</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="3895725"/>
+    <ext cx="2286000" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="71" name="Image 71" descr="Picture"/>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="312.75" customHeight="1">
+    <row r="2" ht="373.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>EL-01</t>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="312.75" customHeight="1">
+    <row r="3" ht="141" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>EL-02</t>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr"/>
     </row>
-    <row r="4" ht="312.75" customHeight="1">
+    <row r="4" ht="141" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EL-03</t>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="312.75" customHeight="1">
+    <row r="5" ht="141" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>EL-04</t>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr"/>
     </row>
-    <row r="6" ht="312.75" customHeight="1">
+    <row r="6" ht="141" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>EL-05</t>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="312.75" customHeight="1">
+    <row r="7" ht="141" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>EL-06</t>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="312.75" customHeight="1">
+    <row r="8" ht="141" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>EL-07</t>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="312.75" customHeight="1">
+    <row r="9" ht="162" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>EL-08</t>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr"/>
     </row>
-    <row r="10" ht="312.75" customHeight="1">
+    <row r="10" ht="141" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>EL-09</t>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="312.75" customHeight="1">
+    <row r="11" ht="141" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>EL-10</t>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="312.75" customHeight="1">
+    <row r="12" ht="141" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>EL-11</t>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="312.75" customHeight="1">
+    <row r="13" ht="141" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>EL-12</t>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr"/>
     </row>
-    <row r="14" ht="312.75" customHeight="1">
+    <row r="14" ht="141" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>EL-13</t>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="312.75" customHeight="1">
+    <row r="15" ht="141" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>EL-14</t>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr"/>
     </row>
-    <row r="16" ht="312.75" customHeight="1">
+    <row r="16" ht="141" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>EL-15</t>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="312.75" customHeight="1">
+    <row r="17" ht="373.5" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>EL-16</t>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr"/>
     </row>
-    <row r="18" ht="312.75" customHeight="1">
+    <row r="18" ht="141" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>EL-17</t>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="312.75" customHeight="1">
+    <row r="19" ht="145.5" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>EL-18</t>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr"/>
     </row>
-    <row r="20" ht="312.75" customHeight="1">
+    <row r="20" ht="141" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>EL-19</t>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr"/>
     </row>
-    <row r="21" ht="312.75" customHeight="1">
+    <row r="21" ht="141" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>EL-20</t>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="312.75" customHeight="1">
+    <row r="22" ht="141" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>EL-21</t>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr"/>
     </row>
-    <row r="23" ht="312.75" customHeight="1">
+    <row r="23" ht="141" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>EL-22</t>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr"/>
     </row>
-    <row r="24" ht="312.75" customHeight="1">
+    <row r="24" ht="373.5" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>EL-23</t>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="312.75" customHeight="1">
+    <row r="25" ht="141" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>EL-24</t>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr"/>
     </row>
-    <row r="26" ht="312.75" customHeight="1">
+    <row r="26" ht="141" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>EL-25</t>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="312.75" customHeight="1">
+    <row r="27" ht="141" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>EL-26</t>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr"/>
     </row>
-    <row r="28" ht="312.75" customHeight="1">
+    <row r="28" ht="141" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>EL-27</t>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr"/>
     </row>
-    <row r="29" ht="312.75" customHeight="1">
+    <row r="29" ht="141" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>EL-28</t>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr"/>
     </row>
-    <row r="30" ht="312.75" customHeight="1">
+    <row r="30" ht="141" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>EL-29</t>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="312.75" customHeight="1">
+    <row r="31" ht="141" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>EL-30</t>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr"/>
     </row>
-    <row r="32" ht="312.75" customHeight="1">
+    <row r="32" ht="141" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>EL-31</t>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr"/>
     </row>
-    <row r="33" ht="312.75" customHeight="1">
+    <row r="33" ht="141" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>EL-32</t>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr"/>
     </row>
-    <row r="34" ht="312.75" customHeight="1">
+    <row r="34" ht="141" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>EL-33</t>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr"/>
     </row>
-    <row r="35" ht="312.75" customHeight="1">
+    <row r="35" ht="141" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>EL-34</t>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr"/>
     </row>
-    <row r="36" ht="312.75" customHeight="1">
+    <row r="36" ht="141" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>EL-35</t>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr"/>
     </row>
-    <row r="37" ht="312.75" customHeight="1">
+    <row r="37" ht="141" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>EL-36</t>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr"/>
     </row>
-    <row r="38" ht="312.75" customHeight="1">
+    <row r="38" ht="141" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>EL-37</t>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
     </row>
-    <row r="39" ht="312.75" customHeight="1">
+    <row r="39" ht="141" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>EL-38</t>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr"/>
     </row>
-    <row r="40" ht="312.75" customHeight="1">
+    <row r="40" ht="141" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>EL-39</t>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr"/>
     </row>
-    <row r="41" ht="312.75" customHeight="1">
+    <row r="41" ht="141" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>EL-40</t>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr"/>
     </row>
-    <row r="42" ht="312.75" customHeight="1">
+    <row r="42" ht="141" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>EL-41</t>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
     </row>
-    <row r="43" ht="312.75" customHeight="1">
+    <row r="43" ht="141" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>EL-42</t>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
     </row>
-    <row r="44" ht="312.75" customHeight="1">
+    <row r="44" ht="141" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>EL-43</t>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
     </row>
-    <row r="45" ht="312.75" customHeight="1">
+    <row r="45" ht="373.5" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>EL-44</t>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr"/>
     </row>
-    <row r="46" ht="312.75" customHeight="1">
+    <row r="46" ht="141" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>EL-45</t>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr"/>
     </row>
-    <row r="47" ht="312.75" customHeight="1">
+    <row r="47" ht="373.5" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>EL-46</t>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr"/>
     </row>
-    <row r="48" ht="312.75" customHeight="1">
+    <row r="48" ht="141" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>EL-47</t>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr"/>
     </row>
-    <row r="49" ht="312.75" customHeight="1">
+    <row r="49" ht="211.5" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>EL-48</t>
@@ -10535,7 +10535,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr"/>
     </row>
-    <row r="50" ht="312.75" customHeight="1">
+    <row r="50" ht="141" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>EL-49</t>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
     </row>
-    <row r="51" ht="312.75" customHeight="1">
+    <row r="51" ht="141" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>EL-50</t>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
     </row>
-    <row r="52" ht="312.75" customHeight="1">
+    <row r="52" ht="141" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>EL-51</t>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
     </row>
-    <row r="53" ht="312.75" customHeight="1">
+    <row r="53" ht="141" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>EL-52</t>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr"/>
     </row>
-    <row r="54" ht="312.75" customHeight="1">
+    <row r="54" ht="141" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>EL-53</t>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr"/>
     </row>
-    <row r="55" ht="312.75" customHeight="1">
+    <row r="55" ht="141" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>EL-54</t>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr"/>
     </row>
-    <row r="56" ht="312.75" customHeight="1">
+    <row r="56" ht="373.5" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>EL-55</t>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr"/>
     </row>
-    <row r="57" ht="312.75" customHeight="1">
+    <row r="57" ht="141" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>EL-56</t>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr"/>
     </row>
-    <row r="58" ht="312.75" customHeight="1">
+    <row r="58" ht="141" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>EL-57</t>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr"/>
     </row>
-    <row r="59" ht="312.75" customHeight="1">
+    <row r="59" ht="141" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>EL-58</t>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr"/>
     </row>
-    <row r="60" ht="312.75" customHeight="1">
+    <row r="60" ht="141" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>EL-59</t>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr"/>
     </row>
-    <row r="61" ht="312.75" customHeight="1">
+    <row r="61" ht="141" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>EL-60</t>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr"/>
     </row>
-    <row r="62" ht="312.75" customHeight="1">
+    <row r="62" ht="141" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>EL-61</t>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr"/>
     </row>
-    <row r="63" ht="312.75" customHeight="1">
+    <row r="63" ht="373.5" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>EL-62</t>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr"/>
     </row>
-    <row r="64" ht="312.75" customHeight="1">
+    <row r="64" ht="141" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>EL-63</t>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr"/>
     </row>
-    <row r="65" ht="312.75" customHeight="1">
+    <row r="65" ht="141" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>EL-64</t>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr"/>
     </row>
-    <row r="66" ht="312.75" customHeight="1">
+    <row r="66" ht="141" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>EL-65</t>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr"/>
     </row>
-    <row r="67" ht="312.75" customHeight="1">
+    <row r="67" ht="141" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>EL-66</t>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr"/>
     </row>
-    <row r="68" ht="312.75" customHeight="1">
+    <row r="68" ht="141" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>EL-67</t>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr"/>
     </row>
-    <row r="69" ht="312.75" customHeight="1">
+    <row r="69" ht="141" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>EL-68</t>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr"/>
     </row>
-    <row r="70" ht="312.75" customHeight="1">
+    <row r="70" ht="141" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>EL-69</t>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" ht="312.75" customHeight="1">
+    <row r="71" ht="141" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>EL-70</t>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr"/>
     </row>
-    <row r="72" ht="312.75" customHeight="1">
+    <row r="72" ht="141" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>EL-71</t>
